--- a/Excel/Level.xlsx
+++ b/Excel/Level.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\42421\Desktop\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4165AE57-6FF4-4738-9E04-A69B2ED6E620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06736F2-8426-44EF-9DD4-B3086DDC5C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Level" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,10 +96,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>vector2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -168,6 +164,10 @@
   </si>
   <si>
     <t>hpValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -525,13 +525,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -593,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>14</v>
@@ -601,40 +601,40 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -673,7 +673,7 @@
         <v>0.7</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M5" s="1">
         <v>200</v>
@@ -714,7 +714,7 @@
         <v>0.7</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M6" s="1">
         <v>250</v>
@@ -756,7 +756,7 @@
         <v>0.7</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M7" s="1">
         <v>350</v>
@@ -797,7 +797,7 @@
         <v>0.7</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M8" s="1">
         <v>500</v>
@@ -839,7 +839,7 @@
         <v>0.7</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M9" s="1">
         <v>800</v>
@@ -881,7 +881,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M10" s="1">
         <v>200</v>
@@ -923,7 +923,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M11" s="1">
         <v>250</v>
@@ -965,7 +965,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M12" s="1">
         <v>300</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M13" s="1">
         <v>400</v>
@@ -1049,7 +1049,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M14" s="1">
         <v>600</v>
@@ -1091,7 +1091,7 @@
         <v>0.5</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M15" s="1">
         <v>400</v>
@@ -1133,7 +1133,7 @@
         <v>0.5</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M16" s="1">
         <v>500</v>
@@ -1175,7 +1175,7 @@
         <v>0.5</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M17" s="1">
         <v>600</v>
@@ -1217,7 +1217,7 @@
         <v>0.5</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M18" s="1">
         <v>750</v>
@@ -1259,7 +1259,7 @@
         <v>0.5</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M19" s="1">
         <v>900</v>
